--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,37 +430,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
@@ -597,7 +609,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -632,17 +644,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>ECOGREEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>ECOGREEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -667,7 +679,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4641,37 +4653,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,37 +418,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
@@ -609,7 +597,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,17 +632,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -679,7 +667,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4653,37 +4641,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Audit matching" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Da verificare" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,41 +414,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>
@@ -609,7 +597,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,17 +632,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOGREEN</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -679,7 +667,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3129,12 +3117,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3147,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3182,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3217,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3252,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3287,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3322,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3357,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3392,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3427,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3462,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3497,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3532,17 +3520,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3572,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3602,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3637,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3672,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3707,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3742,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3777,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3812,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3847,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3882,12 +3870,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3899,12 +3887,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3917,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3952,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3969,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3987,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4022,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4057,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4092,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4127,141 +4115,141 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>EPSILON TORO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>EPSILON TORO SRL</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO SRL</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>SOLUX</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>SOLUX SRL</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>EF AGRI AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Milano Ovest</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4274,29 +4262,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4309,12 +4297,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4326,12 +4314,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4344,29 +4332,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4379,29 +4367,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4414,17 +4402,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -4466,12 +4454,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4484,29 +4472,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4519,29 +4507,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4554,29 +4542,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4589,12 +4577,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4606,33 +4594,103 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
@@ -4653,37 +4711,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cliente progetto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente normalizzato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Esito matching</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Miglior candidato</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cliente report abbinato</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Filiale cliente</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4202,33 +4202,47 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MENINAS</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MENINAS SRL</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4244,47 +4258,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>SOLUX</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>SOLUX SRL</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4297,29 +4297,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4332,29 +4332,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4367,29 +4367,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4402,29 +4402,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4524,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4542,29 +4542,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4612,29 +4612,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,50 +4647,190 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4237,33 +4237,47 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>REN UP</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>REN UP SRL</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4279,47 +4293,33 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>SOLUX</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>SOLUX SRL</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4332,29 +4332,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4367,29 +4367,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4402,29 +4402,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -4524,12 +4524,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4542,29 +4542,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4612,29 +4612,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,29 +4647,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4717,29 +4717,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,29 +4752,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,50 +4787,85 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2977,12 +2977,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,34 +3030,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3082,17 +3082,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3432,12 +3432,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4027,12 +4027,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,50 +4255,64 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>REN UP</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>REN UP SRL</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4314,47 +4328,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>SOLUX</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>SOLUX SRL</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4367,29 +4367,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4402,29 +4402,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4472,29 +4472,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4612,29 +4612,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,29 +4647,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4717,29 +4717,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,29 +4752,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,29 +4787,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4822,50 +4822,85 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1892,12 +1892,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3082,17 +3082,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,34 +3170,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3222,12 +3222,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3502,12 +3502,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,17 +3555,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3607,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4027,12 +4027,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,71 +4290,99 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO SRL</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>MENINAS</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MENINAS SRL</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4367,99 +4395,71 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>EF AGRI AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Milano Ovest</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4472,29 +4472,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4507,29 +4507,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4542,29 +4542,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4577,29 +4577,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4612,29 +4612,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,17 +4647,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4699,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4717,29 +4717,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4769,12 +4769,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4804,12 +4804,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4822,29 +4822,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4857,50 +4857,225 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3117,12 +3117,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,17 +3187,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,34 +3275,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3607,12 +3607,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,71 +4395,99 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ELEMENTS CODIGORO SRL</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MENINAS</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>MENINAS SRL</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4472,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4507,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4542,12 +4570,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4559,82 +4587,54 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>OPEN SOLAR 3</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>OPEN SOLAR 3 SRL</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Milano Sud</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>SORGENIA RENEWABLES</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>SORGENIA RENEWABLES SRL</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Milano Ovest</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,29 +4647,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4717,29 +4717,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4769,12 +4769,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,29 +4787,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4822,29 +4822,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4857,29 +4857,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4892,29 +4892,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4927,29 +4927,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4979,12 +4979,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4997,29 +4997,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5032,50 +5032,260 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3222,12 +3222,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,34 +3275,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,34 +3345,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3887,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,71 +4570,99 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>REN UP</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>REN UP SRL</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>HF SOLAR 18</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>HF SOLAR 18 SRL</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Catania</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4647,99 +4675,71 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>skynrg srl</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SKYNRG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>EF AGRI AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Milano Ovest</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>t.e.a.. gest srl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>T A GEST</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
-        </is>
-      </c>
+          <t>ESCLUSO_DA_CONFIG</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,29 +4752,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4804,12 +4804,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4822,29 +4822,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4857,29 +4857,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4892,29 +4892,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4927,29 +4927,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4962,17 +4962,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5032,29 +5032,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5084,12 +5084,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5102,29 +5102,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5137,29 +5137,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5172,29 +5172,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5207,29 +5207,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5259,33 +5259,208 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4692,54 +4692,82 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>skynrg srl</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SKYNRG</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO SRL</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>t.e.a.. gest srl</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>T A GEST</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>SOLUX</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SOLUX SRL</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4752,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4787,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4822,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4857,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4892,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4927,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4962,17 +4990,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5042,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5032,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5067,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5102,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5137,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5172,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5207,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5242,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5277,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5312,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5347,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5382,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>FLYSUN 10</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>FLYSUN 10 SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5417,50 +5445,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>EGP MAZZOCCHIO SRL</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>EGP MAZZOCCHIO</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>EGP MAZZOCCHIO</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>EGP MAZZOCCHIO SRL</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
@@ -5477,7 +5470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5517,48 +5510,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>skynrg srl</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SKYNRG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>t.e.a.. gest srl</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>T A GEST</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ESCLUSO_DA_CONFIG</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3607,12 +3607,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3747,12 +3747,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4482,12 +4482,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5357,12 +5357,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,50 +5410,120 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,12 +1927,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2347,12 +2347,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2382,12 +2382,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2837,12 +2837,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3362,17 +3362,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3397,17 +3397,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4377,12 +4377,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,17 +5060,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5112,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,50 +5480,85 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1962,12 +1962,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2102,12 +2102,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,17 +2330,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2417,12 +2417,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,34 +3380,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3432,12 +3432,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3537,12 +3537,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,34 +3555,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4272,12 +4272,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4307,12 +4307,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5042,12 +5042,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5077,12 +5077,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5322,12 +5322,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5427,12 +5427,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5462,12 +5462,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,50 +5515,295 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,12 +562,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>AG 31 SRL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>AG 31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -580,29 +580,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>AG 31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>AG 31 SRL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -615,29 +615,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -667,12 +667,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -702,12 +702,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -755,29 +755,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -790,29 +790,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -825,29 +825,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -860,29 +860,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -895,29 +895,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -965,29 +965,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1035,29 +1035,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1122,12 +1122,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1140,29 +1140,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1280,29 +1280,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1350,29 +1350,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,29 +1385,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1455,29 +1455,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1542,12 +1542,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,29 +1875,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1927,12 +1927,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1962,12 +1962,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1997,12 +1997,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,29 +2015,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,17 +2365,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2662,12 +2662,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2942,12 +2942,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3572,17 +3572,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3607,17 +3607,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4027,12 +4027,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4797,12 +4797,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,17 +5340,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,50 +5760,85 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3502,12 +3502,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3607,17 +3607,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,17 +3642,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,12 +3817,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4692,12 +4692,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,17 +5375,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,50 +5795,85 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,12 +597,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>CUBICO NORA SRL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>CUBICO NORA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -615,29 +615,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>CUBICO NORA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>CUBICO NORA SRL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,29 +650,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -702,12 +702,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -790,29 +790,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -825,29 +825,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -860,29 +860,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -895,29 +895,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,29 +930,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -982,12 +982,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1035,29 +1035,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1157,12 +1157,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1175,29 +1175,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1280,29 +1280,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1350,29 +1350,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,29 +1385,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1455,29 +1455,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1577,12 +1577,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1892,12 +1892,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1962,12 +1962,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1997,12 +1997,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2662,12 +2662,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2977,12 +2977,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,34 +3625,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,34 +3695,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4307,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5322,12 +5322,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5392,12 +5392,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,17 +5515,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,50 +5830,155 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,12 +2102,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,17 +2435,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2522,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2662,12 +2662,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3222,12 +3222,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3362,12 +3362,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3712,17 +3712,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3747,17 +3747,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4167,12 +4167,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,17 +5375,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,17 +5620,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -5672,12 +5672,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5847,12 +5847,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,50 +5935,155 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,12 +2137,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3397,12 +3397,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3747,17 +3747,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3782,17 +3782,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3800,29 +3800,29 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4867,12 +4867,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,17 +5480,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
@@ -5532,12 +5532,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5777,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5952,12 +5952,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,50 +6040,155 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,12 +632,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>TRAIANO SRL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>TRAIANO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,29 +650,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ECOPIU</t>
+          <t>TRAIANO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ECOPIU SRL</t>
+          <t>TRAIANO SRL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -685,29 +685,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECOPIU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECOPIU SRL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ECO GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ECO GREEN SRL</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -737,12 +737,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LA FORMICA</t>
+          <t>ECO GREEN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LA FORMICA SRL</t>
+          <t>ECO GREEN SRL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -772,12 +772,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
+          <t>LA FORMICA SRL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -807,12 +807,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -825,29 +825,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>MANNINI IMMOBILIARE TECNOLOGY GREEN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -860,29 +860,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -895,29 +895,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,29 +930,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -965,29 +965,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1017,12 +1017,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1035,29 +1035,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1140,29 +1140,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1210,29 +1210,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1350,29 +1350,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,29 +1385,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1455,29 +1455,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1612,12 +1612,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,29 +1875,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1927,12 +1927,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1997,12 +1997,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2067,12 +2067,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2837,12 +2837,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3082,12 +3082,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3292,12 +3292,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,29 +3310,29 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3432,12 +3432,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3782,17 +3782,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,17 +3817,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,17 +4430,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4937,12 +4937,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5182,12 +5182,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6057,12 +6057,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,50 +6145,225 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2207,12 +2207,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,29 +2330,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2662,12 +2662,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2767,12 +2767,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2837,12 +2837,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2872,12 +2872,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,29 +3030,29 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,29 +3625,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,17 +3817,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3852,17 +3852,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -4552,12 +4552,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5007,12 +5007,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5252,12 +5252,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6197,12 +6197,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6232,12 +6232,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,50 +6320,120 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" t="inlineStr">
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G172" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3992,12 +3992,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4097,12 +4097,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5077,12 +5077,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5567,12 +5567,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,17 +5865,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5917,12 +5917,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,50 +6390,85 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" t="inlineStr">
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5567,12 +5567,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5602,12 +5602,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,50 +6425,85 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,12 +842,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>SUNPROJECT DEV 6 SRL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>SUNPROJECT DEV 6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -860,29 +860,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALTOBRANDO</t>
+          <t>SUNPROJECT DEV 6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALTOBRANDO SRL</t>
+          <t>SUNPROJECT DEV 6 SRL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -895,29 +895,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>NATURGY RINNOVABILI ITALIA SRL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>NATURGY RINNOVABILI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -930,29 +930,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VARNA SOLAR</t>
+          <t>NATURGY RINNOVABILI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VARNA SOLAR SRL</t>
+          <t>NATURGY RINNOVABILI ITALIA SRL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>SPV ENERGY 4 SRL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>SPV ENERGY 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -965,29 +965,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA</t>
+          <t>SPV ENERGY 4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INE ELIOSMENTA SRL</t>
+          <t>SPV ENERGY 4 SRL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>SPV ENERGY 2 SRL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>SPV ENERGY 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO</t>
+          <t>SPV ENERGY 2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENGIE GRILLO SRL</t>
+          <t>SPV ENERGY 2 SRL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>NATURGY RINNOVABILI ITALIA SRL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>NATURGY RINNOVABILI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1035,29 +1035,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>NATURGY RINNOVABILI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>NATURGY RINNOVABILI ITALIA SRL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>SPV ENERGY E32 SRL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>SPV ENERGY E32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PIROIDE</t>
+          <t>SPV ENERGY E32</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PIROIDE SRL</t>
+          <t>SPV ENERGY E32 SRL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>SPV ENERGY E33 SRL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>SPV ENERGY E33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1105,29 +1105,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11PIU</t>
+          <t>SPV ENERGY E33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11PIU' ENERGIA SRL</t>
+          <t>SPV ENERGY E33 SRL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>EDISON RINNOVABILI SPA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>EDISON RINNOVABILI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1140,29 +1140,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NDTHREE</t>
+          <t>EDISON RINNOVABILI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NDTHREE SRL</t>
+          <t>EDISON RINNOVABILI SPA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1175,29 +1175,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IBVI 5</t>
+          <t>ALTOBRANDO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IBVI 5 SRL</t>
+          <t>ALTOBRANDO SRL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1210,29 +1210,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IBVI 22</t>
+          <t>IBERDROLA RENOVABLES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IBVI 22 SRL</t>
+          <t>IBERDROLA RENOVABLES ITALIA SPA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENNA 1 PV</t>
+          <t>VARNA SOLAR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ENNA 1 PV SRL</t>
+          <t>VARNA SOLAR SRL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1280,29 +1280,29 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENNA 2 PV</t>
+          <t>INE ELIOSMENTA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ENNA 2 PV SRL</t>
+          <t>INE ELIOSMENTA SRL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1315,29 +1315,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ENNA 3 PV</t>
+          <t>ENGIE GRILLO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ENNA 3 PV SRL</t>
+          <t>ENGIE GRILLO SRL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1350,29 +1350,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FRI EL SOLAR</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FRI-EL SOLAR SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,29 +1385,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY</t>
+          <t>PIROIDE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RB SOLAR ENERGY SRL</t>
+          <t>PIROIDE SRL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1420,29 +1420,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
+          <t>11PIU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
+          <t>11PIU' ENERGIA SRL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1455,29 +1455,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CVA EOS</t>
+          <t>NDTHREE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVA EOS SRL</t>
+          <t>NDTHREE SRL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cosenza</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1490,29 +1490,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR</t>
+          <t>IBVI 5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PERIDOT SOLAR (ITALY) SRL</t>
+          <t>IBVI 5 SRL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CCE ITALIA</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CCE</t>
+          <t>IBVI 22</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CCE ITALIA SRL</t>
+          <t>IBVI 22 SRL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,29 +1560,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CAPOBIANCO</t>
+          <t>ENNA 1 PV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CAPOBIANCO SRL</t>
+          <t>ENNA 1 PV SRL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1595,29 +1595,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV</t>
+          <t>ENNA 2 PV</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EDPR SICILIA PV SRL</t>
+          <t>ENNA 2 PV SRL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RENANTIS</t>
+          <t>ENNA 3 PV</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RENANTIS ITALIA SRL</t>
+          <t>ENNA 3 PV SRL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1665,29 +1665,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ARYA SOLAR</t>
+          <t>FRI EL SOLAR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ARYA SOLAR SRL</t>
+          <t>FRI-EL SOLAR SRL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1700,29 +1700,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR</t>
+          <t>RB SOLAR ENERGY</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MUSSOMELI SOLAR SRL</t>
+          <t>RB SOLAR ENERGY SRL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1735,29 +1735,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DELTA SOLAR</t>
+          <t>D2M GREEN ENERGY CONCHE DELL ORO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DELTA SOLAR SRL</t>
+          <t>D2M GREEN ENERGY - CONCHE DELL'ORO SRL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SORGENIA LEO</t>
+          <t>CVA EOS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SORGENIA LEO SRL</t>
+          <t>CVA EOS SRL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1805,29 +1805,29 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>INE SCAVO</t>
+          <t>PERIDOT SOLAR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INE SCAVO SRL</t>
+          <t>PERIDOT SOLAR (ITALY) SRL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>CCE ITALIA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FRIEL SUN</t>
+          <t>CCE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FRIEL SUN SRL</t>
+          <t>CCE ITALIA SRL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1875,29 +1875,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12</t>
+          <t>CAPOBIANCO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ALTA CAPITAL 12 SRL</t>
+          <t>CAPOBIANCO SRL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1910,29 +1910,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>X ELIO ENNA 2</t>
+          <t>EDPR SICILIA PV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>X-ELIO ENNA 2 SRL</t>
+          <t>EDPR SICILIA PV SRL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1945,29 +1945,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>RENANTIS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>RENANTIS ITALIA SRL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1980,29 +1980,29 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY</t>
+          <t>ARYA SOLAR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>EUROPEAN ENERGY ITALIA SRL</t>
+          <t>ARYA SOLAR SRL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HF SOLAR 4</t>
+          <t>MUSSOMELI SOLAR</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>HF SOLAR 4 SRL</t>
+          <t>MUSSOMELI SOLAR SRL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2032,12 +2032,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2050,29 +2050,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA</t>
+          <t>DELTA SOLAR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL AUGIA SRL</t>
+          <t>DELTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2085,29 +2085,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA</t>
+          <t>SORGENIA LEO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL LERNA SRL</t>
+          <t>SORGENIA LEO SRL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>X ELIO 6</t>
+          <t>INE SCAVO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>X ELIO ITALIA 6 SRL</t>
+          <t>INE SCAVO SRL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2137,12 +2137,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2155,29 +2155,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR</t>
+          <t>FRIEL SUN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RAMACCA AGRISOLAR SRL</t>
+          <t>FRIEL SUN SRL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2190,29 +2190,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TROINA SOLAR</t>
+          <t>ALTA CAPITAL 12</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TROINA SOLAR SRL</t>
+          <t>ALTA CAPITAL 12 SRL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>XELIO ANTARES</t>
+          <t>X ELIO ENNA 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>XELIO ANTARES SRL</t>
+          <t>X-ELIO ENNA 2 SRL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2242,12 +2242,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2260,29 +2260,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2295,29 +2295,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>EUROPEAN ENERGY</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>EUROPEAN ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>HF SOLAR 4</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>HF SOLAR 4 SRL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2365,29 +2365,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>CONTOURGLOBAL AUGIA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>CONTOURGLOBAL AUGIA SRL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2400,29 +2400,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>CONTOURGLOBAL LERNA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>CONTOURGLOBAL LERNA SRL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>X ELIO 6</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>X ELIO ITALIA 6 SRL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2470,29 +2470,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>RAMACCA AGRISOLAR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>RAMACCA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2505,29 +2505,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>TROINA SOLAR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>TROINA SOLAR SRL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,29 +2540,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>XELIO ANTARES</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>XELIO ANTARES SRL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>DREN SOLARE 10</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>DREN SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Brescia</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,29 +2890,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3117,12 +3117,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3152,12 +3152,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,29 +3170,29 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,29 +3205,29 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,29 +3345,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3397,12 +3397,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,12 +3817,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3852,17 +3852,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,29 +4185,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4342,12 +4342,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4377,47 +4377,39 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>NON_TROVATO</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OGR</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>OGR SRL</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Cuneo</t>
-        </is>
-      </c>
+          <t>AGRICOLA AGRI POWER</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4422,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4457,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4492,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4527,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,34 +4562,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4605,29 +4597,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4632,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4667,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4702,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4737,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4772,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4807,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4842,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4877,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4912,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4947,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4982,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,12 +5017,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5042,12 +5034,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5052,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5087,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,12 +5122,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5147,12 +5139,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5157,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5192,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5227,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,12 +5262,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5287,12 +5279,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5297,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5332,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5367,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5402,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5437,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5472,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5507,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5542,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5577,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5612,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5647,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5682,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5717,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5752,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5787,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5822,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5857,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,12 +5892,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5917,12 +5909,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,12 +5927,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5952,12 +5944,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5962,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,12 +5997,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6022,12 +6014,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6032,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6067,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6102,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6137,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6172,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6207,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6242,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6277,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6312,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6347,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6382,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6417,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,50 +6452,1240 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TEP RENEWABLES FERRARA PV</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>TEP RENEWABLES FERRARA PV</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>JUWI ENERGIE RINNOVABILI</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>JUWI ENERGIE RINNOVABILI</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>TEAGRI SOLARE 1 SRL</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TEAGRI SOLARE 1</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>TEAGRI SOLARE 1</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>TEAGRI SOLARE 1 SRL</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ARIAN SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ARIAN SOLAR</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ARIAN SOLAR</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ARIAN SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO SRL</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>LIO ENERGY BUBO SRL</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SOLUX SRL</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SOLUX</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>SOLUX</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>SOLUX SRL</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EF AGRI AGRICOLA A RL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>EF AGRI AGRICOLA A RL</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES SRL</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES SRL</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>HABEMUS SRL</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HABEMUS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>HABEMUS</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>HABEMUS SRL</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>OPEN SOLAR 3 SRL</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>OPEN SOLAR 3</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>OPEN SOLAR 3</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>OPEN SOLAR 3 SRL</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES SRL</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>SORGENIA RENEWABLES SRL</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DS ITALIA 56 SRL</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>DS 56</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>DS 56</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>DS ITALIA 56 SRL</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Roma Aurelia</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SOLE PV SOLAR 3 SRL</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SOLE PV SOLAR 3</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>SOLE PV SOLAR 3</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>SOLE PV SOLAR 3 SRL</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CONTOURGLOBAL CERASUS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CONTOURGLOBAL CERASUS</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>AUKERA ITALY 9 SRL</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>AUKERA 9</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AUKERA 9</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>AUKERA ITALY 9 SRL</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FLYSUN 5 SRL</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>FLYSUN 5</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>FLYSUN 5</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>FLYSUN 5 SRL</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>EG MARCO POLO SRL</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>EG MARCO POLO</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>EG MARCO POLO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>EG MARCO POLO SRL</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SCOTTA SPA</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SCOTTA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SCOTTA</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>SCOTTA SPA</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SHELL ENERGY ITALIA SRL</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Milano Nord</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29 SRL</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>AMBRA SOLARE 29 SRL</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Roma Nomentana</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>FIMENERGIA</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>FIMENERGIA SRL</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM SRL</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>PSG ENERGY SYSTEM SRL</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9 SRL</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>MARMARIA SOLARE 9 SRL</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Roma Nomentana</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>HOPE SRL</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>REN 176</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>REN 176 SRL</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>MGM SOLAR</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>MGM SOLAR SRL</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Cuneo</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ECOPIEDMONT 1 SRL</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Milano Sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="inlineStr">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>
@@ -6520,7 +7702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6560,6 +7742,33 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ALTEA GREEN POWER SPA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALTEA GREEN POWER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NON_TROVATO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AGRICOLA AGRI POWER</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -4387,19 +4387,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NON_TROVATO</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+          <t>ALTEA GREEN POWER</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ALTEA GREEN POWER SPA</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7702,7 +7710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7742,33 +7750,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ALTEA GREEN POWER SPA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ALTEA GREEN POWER</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NON_TROVATO</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AGRICOLA AGRI POWER</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6652,12 +6652,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7002,12 +7002,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,17 +7020,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -7072,12 +7072,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,50 +7650,85 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" t="inlineStr">
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7037,12 +7037,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7212,12 +7212,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7562,12 +7562,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,50 +7685,120 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>1</v>
-      </c>
-      <c r="E209" t="inlineStr">
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6617,12 +6617,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7282,12 +7282,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,50 +7755,155 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SEGNALETICA NOVARESE SRL</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Milano Ovest</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>1</v>
-      </c>
-      <c r="E211" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7842,12 +7842,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,50 +7860,85 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" t="inlineStr">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G215"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6162,12 +6162,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6267,12 +6267,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6617,12 +6617,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,17 +6635,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6862,12 +6862,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,17 +7125,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -7177,12 +7177,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,17 +7195,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
@@ -7247,12 +7247,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,50 +7895,85 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ALPENFRUT</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udine</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>1</v>
-      </c>
-      <c r="E215" t="inlineStr">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5707,12 +5707,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6092,12 +6092,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7387,12 +7387,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,50 +7930,155 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" t="inlineStr">
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4832,12 +4832,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4937,12 +4937,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6162,12 +6162,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6372,12 +6372,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6722,12 +6722,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,17 +6740,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -6792,12 +6792,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6967,12 +6967,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7212,12 +7212,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7282,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7457,12 +7457,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7597,12 +7597,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7877,12 +7877,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7912,12 +7912,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,50 +8035,120 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" t="inlineStr">
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4412,12 +4412,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4447,12 +4447,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,34 +4570,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4622,17 +4622,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6197,12 +6197,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,17 +6775,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -6827,12 +6827,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7527,12 +7527,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7667,12 +7667,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7947,12 +7947,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7982,12 +7982,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,50 +8105,120 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>ELLOMAY SOLAR ELEVEN</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" t="inlineStr">
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2592,12 +2592,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2610,29 +2610,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SOLARANTO</t>
+          <t>TEP RENEWABLES CARLENTINI PV</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SOLARANTO SRL</t>
+          <t>TEP RENEWABLES (CARLENTINI PV) SRL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2645,29 +2645,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SCS 11</t>
+          <t>RENANTIS SICILIA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SCS 11 SRL</t>
+          <t>RENANTIS SICILIA SRL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2680,29 +2680,29 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10</t>
+          <t>SOLARANTO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FLYNIS PV 10 SRL</t>
+          <t>SOLARANTO SRL</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3</t>
+          <t>SCS 11</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DEVELOPMENT 3 SRL</t>
+          <t>SCS 11 SRL</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2750,29 +2750,29 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MARSEGLIA SVILUPPO</t>
+          <t>FLYNIS PV 10</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
+          <t>FLYNIS PV 10 SRL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2785,29 +2785,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 7</t>
+          <t>DEVELOPMENT 3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
+          <t>DEVELOPMENT 3 SRL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1</t>
+          <t>MARSEGLIA SVILUPPO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRINDISI SOLAR 1 SRL</t>
+          <t>MARSEGLIA ENERGIA E SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Venezia</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO</t>
+          <t>GRUPOTEC SOLAR 7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SOLAR ENERGY QUATTRO SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 7 SRL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SY04</t>
+          <t>BRINDISI SOLAR 1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SY04 SRL</t>
+          <t>BRINDISI SOLAR 1 SRL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2907,12 +2907,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SOLAR ENERGY QUATTRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SOLAR ENERGY QUATTRO SRL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2960,17 +2960,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>SY04</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>SY04 SRL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>STATKRAFT</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>STATKRAFT ITALIA SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3065,29 +3065,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES HOLDING</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3100,29 +3100,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH</t>
+          <t>STATKRAFT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AGRI NEW TECH ITALIA SRL</t>
+          <t>STATKRAFT ITALIA SRL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3135,29 +3135,29 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10</t>
+          <t>EDP RENEWABLES HOLDING</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 10 SRL</t>
+          <t>EDP RENEWABLES ITALIA HOLDING SRL</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16</t>
+          <t>AGRI NEW TECH</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 16 SRL</t>
+          <t>AGRI NEW TECH ITALIA SRL</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44</t>
+          <t>MARMARIA SOLARE 10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 44 SRL</t>
+          <t>MARMARIA SOLARE 10 SRL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3222,12 +3222,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17</t>
+          <t>AMBRA SOLARE 16</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 17 SRL</t>
+          <t>AMBRA SOLARE 16 SRL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3257,12 +3257,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3275,29 +3275,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15</t>
+          <t>AMBRA SOLARE 44</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 15 SRL</t>
+          <t>AMBRA SOLARE 44 SRL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40</t>
+          <t>AMBRA SOLARE 17</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 40 SRL</t>
+          <t>AMBRA SOLARE 17 SRL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IOTA PEGASO</t>
+          <t>AMBRA SOLARE 15</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>IOTA PEGASO SRL</t>
+          <t>AMBRA SOLARE 15 SRL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3362,12 +3362,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3380,29 +3380,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 2</t>
+          <t>AMBRA SOLARE 40</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
+          <t>AMBRA SOLARE 40 SRL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3415,29 +3415,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE</t>
+          <t>IOTA PEGASO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RINNOVABILI SUD TRE SRL</t>
+          <t>IOTA PEGASO SRL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Salerno</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3450,29 +3450,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA</t>
+          <t>GRUPOTEC SOLAR 2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LUMINORA MARANGIOSA SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 2 SRL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3485,29 +3485,29 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II</t>
+          <t>RINNOVABILI SUD TRE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BLUE STONE RENEWABLE II SRL</t>
+          <t>RINNOVABILI SUD TRE SRL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Salerno</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3520,29 +3520,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>X ELIO TARAS</t>
+          <t>LUMINORA MARANGIOSA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>X ELIO TARAS SRL</t>
+          <t>LUMINORA MARANGIOSA SRL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>BLUE STONE RENEWABLE II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>BLUE STONE RENEWABLE II SRL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3590,29 +3590,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR</t>
+          <t>X ELIO TARAS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ROCCHETTA SOLAR SRL</t>
+          <t>X ELIO TARAS SRL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SKI 02</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SKI 02 SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3642,12 +3642,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3660,29 +3660,29 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1</t>
+          <t>ROCCHETTA SOLAR</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
+          <t>ROCCHETTA SOLAR SRL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN VI</t>
+          <t>SKI 02</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
+          <t>SKI 02 SRL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,29 +3730,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI</t>
+          <t>BLUSOLAR MIGLIONICO 1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ARNG SOLAR XI SRL</t>
+          <t>BLUSOLAR MIGLIONICO 1 SRL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3765,29 +3765,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1</t>
+          <t>ABEI ENERGY GREEN VI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MAXIMA PV 1 SRL</t>
+          <t>ABEI ENERGY GREEN ITALY VI SRL</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>ARNG SOLAR XI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SANTA BARBARA ENERGIA SRL</t>
+          <t>ARNG SOLAR XI SRL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3817,12 +3817,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3835,29 +3835,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR 3</t>
+          <t>MAXIMA PV 1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
+          <t>MAXIMA PV 1 SRL</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3870,29 +3870,29 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ELIOS</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ELIOS SRL</t>
+          <t>SANTA BARBARA ENERGIA SRL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3905,29 +3905,29 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EOR POWER</t>
+          <t>GRUPOTEC SOLAR 3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EOR POWER SRL</t>
+          <t>GRUPOTEC SOLAR ITALIA 3 SRL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3940,29 +3940,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3</t>
+          <t>ELIOS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>OPDENERGY SALENTO 3 SRL</t>
+          <t>ELIOS SRL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3975,29 +3975,29 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO</t>
+          <t>EOR POWER</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRINA SOLAR PAPIRO SRL</t>
+          <t>EOR POWER SRL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA</t>
+          <t>OPDENERGY SALENTO 3</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ENERGETICA SALENTINA SRL</t>
+          <t>OPDENERGY SALENTO 3 SRL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4045,29 +4045,29 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA</t>
+          <t>TRINA SOLAR PAPIRO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>APOLLO FOGGIA SRL</t>
+          <t>TRINA SOLAR PAPIRO SRL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4080,29 +4080,29 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HEPV12</t>
+          <t>ENERGETICA SALENTINA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HEPV12 SRL</t>
+          <t>ENERGETICA SALENTINA SRL</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bari</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4115,29 +4115,29 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32</t>
+          <t>APOLLO FOGGIA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 32 SRL</t>
+          <t>APOLLO FOGGIA SRL</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MYSUN</t>
+          <t>HEPV12</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MYSUN SRL</t>
+          <t>HEPV12 SRL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HF SOLAR 8</t>
+          <t>AMBRA SOLARE 32</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HF SOLAR 8 SRL</t>
+          <t>AMBRA SOLARE 32 SRL</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4220,29 +4220,29 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>MYSUN</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>MYSUN SRL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,29 +4255,29 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>HF SOLAR 8</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>HF SOLAR 8 SRL</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>WHYSOLE SVILUPPO SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4325,29 +4325,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IPC PUGLIA</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IPC PUGLIA SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4360,29 +4360,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SOLE VERDE DELLA PRAETORIAN</t>
+          <t>WHYSOLE SVILUPPO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
+          <t>WHYSOLE SVILUPPO SRL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4395,29 +4395,29 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER</t>
+          <t>IPC PUGLIA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ALTEA GREEN POWER SPA</t>
+          <t>IPC PUGLIA SRL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4430,29 +4430,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1</t>
+          <t>SOLE VERDE DELLA PRAETORIAN</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BLUSOLAR GROTTOLE 1 SRL</t>
+          <t>SOLE VERDE SAS DELLA PRAETORIAN SRL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4465,29 +4465,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>ALTEA GREEN POWER</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>ALTEA GREEN POWER SPA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4500,29 +4500,29 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>BLUSOLAR GROTTOLE 1</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>BLUSOLAR GROTTOLE 1 SRL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,29 +4570,29 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4622,17 +4622,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,34 +4675,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,29 +4745,29 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4902,12 +4902,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,29 +4955,29 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5217,12 +5217,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5497,12 +5497,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,29 +5550,29 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,17 +5655,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5707,12 +5707,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,29 +5725,29 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5760,29 +5760,29 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,29 +5935,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6232,12 +6232,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,29 +6285,29 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6547,12 +6547,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,29 +6600,29 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7282,12 +7282,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7422,12 +7422,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7527,12 +7527,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,29 +7685,29 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,29 +7825,29 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,29 +8105,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ELEVEN</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,29 +8140,29 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ALPENFRUT</t>
+          <t>ECOPIEDMONT 1 SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Udine</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8175,50 +8175,155 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>FLYSUN 10</t>
+          <t>SEGNALETICA NOVARESE</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>FLYSUN 10 SRL</t>
+          <t>SEGNALETICA NOVARESE SRL</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ELEVEN</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ELLOMAY SOLAR ITALY ELEVEN SRL</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Bolzano</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ALPENFRUT</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Udine</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>FLYSUN 10</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>FLYSUN 10 SRL</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>ESATTO_NORMALIZZATO</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" t="inlineStr">
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ESATTO_NORMALIZZATO</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>EGP MAZZOCCHIO SRL</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>Frosinone</t>
         </is>

--- a/output/audit_abbinamenti.xlsx
+++ b/output/audit_abbinamenti.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4517,12 +4517,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4535,29 +4535,29 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ICA REN ELF</t>
+          <t>SAN GIORGIO JONICO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ICA REN ELF SRL</t>
+          <t>SAN GIORGIO JONICO SRL</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES</t>
+          <t>SKI 09</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HERGO RENEWABLES SPA</t>
+          <t>SKI 09 SRL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4605,29 +4605,29 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RNE1</t>
+          <t>ICA REN ELF</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RNE1 SRL</t>
+          <t>ICA REN ELF SRL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR</t>
+          <t>HERGO RENEWABLES</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ARDEA AGRISOLAR SRL</t>
+          <t>HERGO RENEWABLES SPA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
+          <t>RNE1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
+          <t>RNE1 SRL</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4692,17 +4692,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ENERGY4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ALIAS</t>
+          <t>ESATTO_NORMALIZZATO</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4710,29 +4710,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ENERGY4U E4U</t>
+          <t>ARDEA AGRISOLAR</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
+          <t>ARDEA AGRISOLAR SRL</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4745,34 +4745,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>GIOJANA</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GIOJANA SRL</t>
+          <t>BALTEX SARDEGNA 10 VILLANOVA TRUSCHEDU SRL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bergamo</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ESATTO_NORMALIZZATO</t>
+          <t>ALIAS</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4780,29 +4780,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>VEN SAR</t>
+          <t>ENERGY4U E4U</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>VEN.SAR. SRL</t>
+          <t>ENERGY4U SRL IN FORMA ABBREVIATO E4U SRL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4815,29 +4815,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR</t>
+          <t>GIOJANA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PV ICHNOSOLAR SRL</t>
+          <t>GIOJANA SRL</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bergamo</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4850,29 +4850,29 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2</t>
+          <t>VEN SAR</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
+          <t>VEN.SAR. SRL</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Cagliari</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4885,29 +4885,29 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO</t>
+          <t>PV ICHNOSOLAR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>DELTA ACQUARIO SRL</t>
+          <t>PV ICHNOSOLAR SRL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4920,29 +4920,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TISI</t>
+          <t>GREEN ENERGY SARDEGNA 2</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TISI SRL</t>
+          <t>GREEN ENERGY SARDEGNA 2 SRL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OPR SUN 8</t>
+          <t>DELTA ACQUARIO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OPR SUN 8 SRL</t>
+          <t>DELTA ACQUARIO SRL</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4972,12 +4972,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4990,29 +4990,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES</t>
+          <t>TISI</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
+          <t>TISI SRL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5025,29 +5025,29 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ASJA SASSARI</t>
+          <t>OPR SUN 8</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ASJA SASSARI SRL</t>
+          <t>OPR SUN 8 SRL</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5060,29 +5060,29 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ASJA NURRA</t>
+          <t>ENI PLENITUDE RENEWABLES</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ASJA NURRA SRL</t>
+          <t>ENI PLENITUDE RENEWABLES ITALY SPA</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5095,29 +5095,29 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR</t>
+          <t>ASJA SASSARI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>QUISTELLA SOLAR SRL</t>
+          <t>ASJA SASSARI SRL</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SONNEDIX</t>
+          <t>ASJA NURRA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SONNEDIX ITALIA SRL</t>
+          <t>ASJA NURRA SRL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5165,29 +5165,29 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS</t>
+          <t>QUISTELLA SOLAR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>LIO ENERGY TAURUS SRL</t>
+          <t>QUISTELLA SOLAR SRL</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Parma</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5200,29 +5200,29 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1</t>
+          <t>SONNEDIX</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
+          <t>SONNEDIX ITALIA SRL</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5235,29 +5235,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>STM26</t>
+          <t>LIO ENERGY TAURUS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>STM26 SRL</t>
+          <t>LIO ENERGY TAURUS SRL</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FRV</t>
+          <t>BLUSOLAR CHIARAVALLE 1</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FRV ITALIA SRL</t>
+          <t>BLUSOLAR CHIARAVALLE 1 SRL</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5287,12 +5287,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BELLOCCHI PV</t>
+          <t>STM26</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
+          <t>STM26 SRL</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5340,29 +5340,29 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ACCIONA GLOBAL</t>
+          <t>FRV</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
+          <t>FRV ITALIA SRL</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5375,29 +5375,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>OGR</t>
+          <t>TEP RENEWABLES BELLOCCHI PV</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OGR SRL</t>
+          <t>TEP RENEWABLES (BELLOCCHI PV) SRL</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE</t>
+          <t>ACCIONA GLOBAL</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SONNEDIX SAN GABRIELE SRL</t>
+          <t>ACCIONA ENERGIA GLOBAL ITALIA SRL</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5445,29 +5445,29 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AGRICOLA AGRI POWER</t>
+          <t>OGR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
+          <t>OGR SRL</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Firenze</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5480,29 +5480,29 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>K2SOLAR</t>
+          <t>SONNEDIX SAN GABRIELE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>K2SOLAR SRL</t>
+          <t>SONNEDIX SAN GABRIELE SRL</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5515,29 +5515,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>REVALUE PV 1</t>
+          <t>AGRICOLA AGRI POWER</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>REVALUE PV 1 SRL</t>
+          <t>SOCIETA' AGRICOLA AGRI - POWER SRL</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Firenze</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES</t>
+          <t>K2SOLAR</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RWE RENEWABLES ITALIA SRL</t>
+          <t>K2SOLAR SRL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5567,12 +5567,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5585,29 +5585,29 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>REVALUE PV 1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>REVALUE PV 1 SRL</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SINERGIA GP12</t>
+          <t>RWE RENEWABLES</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SINERGIA GP12 SRL</t>
+          <t>RWE RENEWABLES ITALIA SRL</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5655,29 +5655,29 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FRANCAVILLA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5690,29 +5690,29 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>SIG PROJECT 1</t>
+          <t>SINERGIA GP12</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SIG PROJECT ITALY 1 SRL</t>
+          <t>SINERGIA GP12 SRL</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ATON 22</t>
+          <t>FRANCAVILLA SOLAR PARK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ATON 22 SRL</t>
+          <t>FRANCAVILLA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5777,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5795,29 +5795,29 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01</t>
+          <t>ATON 22</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>VESPERA DEVELOPMENT 01 SRL</t>
+          <t>ATON 22 SRL</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5830,29 +5830,29 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK</t>
+          <t>SIG PROJECT 1</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>APOLLOSA SOLAR PARK SRL</t>
+          <t>SIG PROJECT ITALY 1 SRL</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5865,29 +5865,29 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>HELIOS ONE</t>
+          <t>VESPERA DEVELOPMENT 01</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>HELIOS ONE SRL</t>
+          <t>VESPERA DEVELOPMENT 01 SRL</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5900,29 +5900,29 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS</t>
+          <t>APOLLOSA SOLAR PARK</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SOLAR BOREALIS SRL</t>
+          <t>APOLLOSA SOLAR PARK SRL</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>MAAG TIMO</t>
+          <t>HELIOS ONE</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MAAG TIMO SRL</t>
+          <t>HELIOS ONE SRL</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5952,12 +5952,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT</t>
+          <t>SOLAR BOREALIS</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ALPICAPITAL DEVELOPMENT SRL</t>
+          <t>SOLAR BOREALIS SRL</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6005,29 +6005,29 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA</t>
+          <t>MAAG TIMO</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ECOENER ALFINA SRL</t>
+          <t>MAAG TIMO SRL</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Napoli</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6040,29 +6040,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ALPICAPITAL DEVELOPMENT</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>GC ITALIA SRL</t>
+          <t>ALPICAPITAL DEVELOPMENT SRL</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Trento</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6075,29 +6075,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AGROVOLT 01</t>
+          <t>ECOENER ALFINA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AGROVOLT 01 SRL</t>
+          <t>ECOENER ALFINA SRL</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6110,29 +6110,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL SAMAS SRL</t>
+          <t>GC ITALIA SRL</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FREE ENERGY</t>
+          <t>AGROVOLT 01</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FREE ENERGY SRL</t>
+          <t>AGROVOLT 01 SRL</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>REVALUE PV 8</t>
+          <t>CONTOURGLOBAL SAMAS</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>REVALUE PV 8 SRL</t>
+          <t>CONTOURGLOBAL SAMAS SRL</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Milano Est</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6215,29 +6215,29 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE</t>
+          <t>FREE ENERGY</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CUBICO CASALONE SRL</t>
+          <t>FREE ENERGY SRL</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>REVALUE PV 8</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>REVALUE PV 8 SRL</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Est</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ZENITH</t>
+          <t>CUBICO CASALONE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ZENITH ENERGIA SRL</t>
+          <t>CUBICO CASALONE SRL</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6320,29 +6320,29 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>M SOLAR</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>R.M. SOLAR SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6355,29 +6355,29 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES BOCCEA PV</t>
+          <t>ZENITH</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
+          <t>ZENITH ENERGIA SRL</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO</t>
+          <t>M SOLAR</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>PACIFICO BERILLO SRL</t>
+          <t>R.M. SOLAR SRL</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>X C SOLAR</t>
+          <t>TEP RENEWABLES BOCCEA PV</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>X.C. SOLAR SRL</t>
+          <t>TEP RENEWABLES (BOCCEA PV) SRL</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>LEA-RENERGY</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6460,29 +6460,29 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>LEA RENERGY</t>
+          <t>PACIFICO BERILLO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>LEA-RENERGY SRL</t>
+          <t>PACIFICO BERILLO SRL</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6495,29 +6495,29 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI</t>
+          <t>X C SOLAR</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ROMAGNA IMPIANTI SRL</t>
+          <t>X.C. SOLAR SRL</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rimini</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>EPSILON TORO</t>
+          <t>LEA RENERGY</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>EPSILON TORO SRL</t>
+          <t>LEA-RENERGY SRL</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6565,29 +6565,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO</t>
+          <t>ROMAGNA IMPIANTI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ELEMENTS CODIGORO SRL</t>
+          <t>ROMAGNA IMPIANTI SRL</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>MENINAS</t>
+          <t>EPSILON TORO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MENINAS SRL</t>
+          <t>EPSILON TORO SRL</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6617,12 +6617,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6635,29 +6635,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>REN UP</t>
+          <t>ELEMENTS CODIGORO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>REN UP SRL</t>
+          <t>ELEMENTS CODIGORO SRL</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6670,29 +6670,29 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HF SOLAR 18</t>
+          <t>MENINAS</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>HF SOLAR 18 SRL</t>
+          <t>MENINAS SRL</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6705,29 +6705,29 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>REN UP</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>REN UP SRL</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6740,29 +6740,29 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES FERRARA PV</t>
+          <t>HF SOLAR 18</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
+          <t>HF SOLAR 18 SRL</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Catania</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6775,29 +6775,29 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>MGM SOLAR</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6810,29 +6810,29 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1</t>
+          <t>TEP RENEWABLES FERRARA PV</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>TEAGRI SOLARE 1 SRL</t>
+          <t>TEP RENEWABLES (FERRARA PV) SRL</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6845,29 +6845,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>ARIAN SOLAR SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6880,29 +6880,29 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>TEAGRI SOLARE 1</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>TEAGRI SOLARE 1 SRL</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6915,29 +6915,29 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ESPE</t>
+          <t>ARIAN SOLAR</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>ESPE SRL</t>
+          <t>ARIAN SOLAR SRL</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6950,29 +6950,29 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>OPR SUN 55</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>OPR SUN 55 SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6985,29 +6985,29 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI</t>
+          <t>ESPE</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JUWI ENERGIE RINNOVABILI SRL</t>
+          <t>ESPE SRL</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7020,29 +7020,29 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO</t>
+          <t>OPR SUN 55</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>LIO ENERGY BUBO SRL</t>
+          <t>OPR SUN 55 SRL</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7055,29 +7055,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA</t>
+          <t>JUWI ENERGIE RINNOVABILI</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>INE LA CASSETTA SRL</t>
+          <t>JUWI ENERGIE RINNOVABILI SRL</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bolzano</t>
+          <t>Verona</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7090,29 +7090,29 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SOLUX</t>
+          <t>LIO ENERGY BUBO</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SOLUX SRL</t>
+          <t>LIO ENERGY BUBO SRL</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7125,29 +7125,29 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>EF AGRI AGRICOLA A RL</t>
+          <t>INE LA CASSETTA</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>EF AGRI SOC AGRICOLA A RL</t>
+          <t>INE LA CASSETTA SRL</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bolzano</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7160,29 +7160,29 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>SOLUX</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>SOLUX SRL</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Bologna</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7195,29 +7195,29 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>HABEMUS</t>
+          <t>EF AGRI AGRICOLA A RL</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>HABEMUS SRL</t>
+          <t>EF AGRI SOC AGRICOLA A RL</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7230,29 +7230,29 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FOTOVOLTAICO SERVICE SRLS</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3</t>
+          <t>HABEMUS</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>OPEN SOLAR 3 SRL</t>
+          <t>HABEMUS SRL</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SORGENIA RENEWABLES SRL</t>
+          <t>FOTOVOLTAICO SERVICE SRLS</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7335,29 +7335,29 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>DS 56</t>
+          <t>OPEN SOLAR 3</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>DS ITALIA 56 SRL</t>
+          <t>OPEN SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Roma Aurelia</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3</t>
+          <t>SORGENIA RENEWABLES</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SOLE PV SOLAR 3 SRL</t>
+          <t>SORGENIA RENEWABLES SRL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7405,29 +7405,29 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS</t>
+          <t>DS 56</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CONTOURGLOBAL CERASUS SRL</t>
+          <t>DS ITALIA 56 SRL</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Aurelia</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>SOLE PV SOLAR 3</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>SOLE PV SOLAR 3 SRL</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7475,29 +7475,29 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>COESA</t>
+          <t>CONTOURGLOBAL CERASUS</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>COESA SRL</t>
+          <t>CONTOURGLOBAL CERASUS SRL</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7510,29 +7510,29 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AUKERA 5</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 5 SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>COESA</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>COESA SRL</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7580,29 +7580,29 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>AUKERA 5</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>AUKERA ITALY 5 SRL</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7615,29 +7615,29 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AUKERA 9</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AUKERA ITALY 9 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>FLYSUN 5</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FLYSUN 5 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>EG MARCO POLO</t>
+          <t>AUKERA 9</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>EG MARCO POLO SRL</t>
+          <t>AUKERA ITALY 9 SRL</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7702,12 +7702,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7720,29 +7720,29 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AG 14</t>
+          <t>FLYSUN 5</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AG 14 SRL</t>
+          <t>FLYSUN 5 SRL</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Padova</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7755,29 +7755,29 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CASTELNOVO</t>
+          <t>EG MARCO POLO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CASTELNOVO SRL</t>
+          <t>EG MARCO POLO SRL</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Milano Nord</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SCOTTA</t>
+          <t>AG 14</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SCOTTA SPA</t>
+          <t>AG 14 SRL</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Padova</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SHELL ENERGY</t>
+          <t>CASTELNOVO</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SHELL ENERGY ITALIA SRL</t>
+          <t>CASTELNOVO SRL</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7842,12 +7842,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7860,29 +7860,29 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29</t>
+          <t>SCOTTA</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AMBRA SOLARE 29 SRL</t>
+          <t>SCOTTA SPA</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Cuneo</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7895,29 +7895,29 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4</t>
+          <t>SHELL ENERGY</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SOLAR CENTURY FVGC 4 SRL</t>
+          <t>SHELL ENERGY ITALIA SRL</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Milano Nord</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7930,29 +7930,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>FIMENERGIA</t>
+          <t>AMBRA SOLARE 29</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FIMENERGIA SRL</t>
+          <t>AMBRA SOLARE 29 SRL</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7965,29 +7965,29 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM</t>
+          <t>SOLAR CENTURY FVGC 4</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>PSG ENERGY SYSTEM SRL</t>
+          <t>SOLAR CENTURY FVGC 4 SRL</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Milano Ovest</t>
+          <t>Milano Sud</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8000,29 +8000,29 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9</t>
+          <t>FIMENERGIA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>MARMARIA SOLARE 9 SRL</t>
+          <t>FIMENERGIA SRL</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Roma Nomentana</t>
+          <t>Torino</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8035,29 +8035,29 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HOPE</t>
+          <t>PSG ENERGY SYSTEM</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>HOPE SRL</t>
+          <t>PSG ENERGY SYSTEM SRL</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Cuneo</t>
+          <t>Milano Ovest</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8070,29 +8070,29 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>REN 176</t>
+          <t>MARMARIA SOLARE 9</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>REN 176 SRL</t>
+          <t>MARMARIA SOLARE 9 SRL</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Milano Sud</t>
+          <t>Roma Nomentana</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>MGM SOLAR</t>
+          <t>HOPE</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>MGM SOLAR SRL</t>
+          <t>HOPE SRL</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -8122,12 +8122,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1</t>
+          <t>REN 176</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>ECOPIEDMONT 1 SRL</t>
+          <t>REN 176 SRL</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8157,12 +8157,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SEGNALETICA NOVARESE SRL</t>
+          <t>MGM SOLAR SRL</t>
         </is>